--- a/data/industry/TrendForce/TFT LCD.xlsx
+++ b/data/industry/TrendForce/TFT LCD.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37D2580C-BC85-4EEE-8E3C-3FFFCE19456F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99DEF56D-AFE2-47A2-BB85-A7D03EF200AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="36">
   <si>
     <t>Large Size Panel</t>
   </si>
@@ -1234,7 +1234,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F72FC54-CD8C-473D-B869-CF3F9FC5C7CC}">
-  <dimension ref="A1:Y7"/>
+  <dimension ref="A1:Y8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="15" bestFit="1" customWidth="1"/>
@@ -1733,6 +1733,80 @@
       </c>
       <c r="X7" s="14">
         <v>161.80000000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A8" s="15">
+        <v>46141</v>
+      </c>
+      <c r="B8" s="15">
+        <v>46141</v>
+      </c>
+      <c r="C8" s="8">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="14">
+        <v>75.099999999999994</v>
+      </c>
+      <c r="F8" s="14">
+        <v>75.099999999999994</v>
+      </c>
+      <c r="G8" s="14">
+        <v>75.099999999999994</v>
+      </c>
+      <c r="H8" s="14">
+        <v>74.599999999999994</v>
+      </c>
+      <c r="I8" s="14">
+        <v>150</v>
+      </c>
+      <c r="J8" s="14">
+        <v>100.6</v>
+      </c>
+      <c r="K8" s="14">
+        <v>102.8</v>
+      </c>
+      <c r="L8" s="14">
+        <v>102.8</v>
+      </c>
+      <c r="M8" s="14">
+        <v>225</v>
+      </c>
+      <c r="N8" s="14">
+        <v>341.3</v>
+      </c>
+      <c r="O8" s="14">
+        <v>317.39999999999998</v>
+      </c>
+      <c r="P8" s="14">
+        <v>302.39999999999998</v>
+      </c>
+      <c r="Q8" s="14">
+        <v>373.1</v>
+      </c>
+      <c r="R8" s="14">
+        <v>428.6</v>
+      </c>
+      <c r="S8" s="14">
+        <v>408.9</v>
+      </c>
+      <c r="T8" s="14">
+        <v>407</v>
+      </c>
+      <c r="U8" s="14">
+        <v>152.9</v>
+      </c>
+      <c r="V8" s="14">
+        <v>208</v>
+      </c>
+      <c r="W8" s="14">
+        <v>168.7</v>
+      </c>
+      <c r="X8" s="14">
+        <v>169.8</v>
       </c>
     </row>
   </sheetData>
@@ -1750,7 +1824,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{535C5E87-C6BF-4E93-9B61-00AC746AD42A}">
-  <dimension ref="A1:Y6"/>
+  <dimension ref="A1:Y7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.09765625" style="15" bestFit="1" customWidth="1"/>
@@ -2063,6 +2137,50 @@
       </c>
       <c r="N6" s="12">
         <v>18066</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A7" s="15">
+        <v>45717</v>
+      </c>
+      <c r="B7" s="15">
+        <v>46133</v>
+      </c>
+      <c r="C7" s="8">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="12">
+        <v>28900</v>
+      </c>
+      <c r="F7" s="12">
+        <v>869</v>
+      </c>
+      <c r="G7" s="12">
+        <v>22860</v>
+      </c>
+      <c r="H7" s="12">
+        <v>1486</v>
+      </c>
+      <c r="I7" s="12">
+        <v>15216</v>
+      </c>
+      <c r="J7" s="12">
+        <v>2934</v>
+      </c>
+      <c r="K7" s="12">
+        <v>21474</v>
+      </c>
+      <c r="L7" s="12">
+        <v>17001</v>
+      </c>
+      <c r="M7" s="12">
+        <v>88450</v>
+      </c>
+      <c r="N7" s="12">
+        <v>22289</v>
       </c>
     </row>
   </sheetData>

--- a/data/industry/TrendForce/TFT LCD.xlsx
+++ b/data/industry/TrendForce/TFT LCD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Geust\PycharmProjects\AlternativeData\data\industry\TrendForce\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{793F4466-66C2-4ED0-86EC-42B553BC57B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32A35781-1A48-4EF8-9799-D1764D7DF65F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="23260" windowHeight="14860" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Large Size Panel" sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="36">
   <si>
     <t>Large Size Panel</t>
   </si>
@@ -180,7 +180,7 @@
     <numFmt numFmtId="167" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -227,6 +227,29 @@
       <name val="Verdana"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -251,7 +274,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -260,48 +283,81 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -579,393 +635,443 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA9EFAE0-DDA9-4895-A6E7-1B8A3730BEB2}">
-  <dimension ref="A1:Y7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <dimension ref="A1:Y8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="12.109375" style="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.109375" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="8" width="9.21875" style="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="25" width="9" style="10"/>
-    <col min="26" max="16384" width="9" style="7"/>
+    <col min="1" max="1" width="9.1796875" style="12" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.7265625" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.08984375" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.81640625" style="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="8" width="9.1796875" style="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="25" width="9" style="15"/>
+    <col min="26" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:25" s="9" customFormat="1">
+      <c r="A1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
-      <c r="V1" s="4"/>
-      <c r="W1" s="4"/>
-      <c r="X1" s="4"/>
-      <c r="Y1" s="4"/>
+      <c r="Q1" s="8"/>
+      <c r="R1" s="8"/>
+      <c r="S1" s="8"/>
+      <c r="T1" s="8"/>
+      <c r="U1" s="8"/>
+      <c r="V1" s="8"/>
+      <c r="W1" s="8"/>
+      <c r="X1" s="8"/>
+      <c r="Y1" s="8"/>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="6" t="s">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="N2" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="O2" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="P2" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
-      <c r="V2" s="6"/>
-      <c r="W2" s="6"/>
-      <c r="X2" s="6"/>
-      <c r="Y2" s="6"/>
+      <c r="Q2" s="10"/>
+      <c r="R2" s="10"/>
+      <c r="S2" s="10"/>
+      <c r="T2" s="10"/>
+      <c r="U2" s="10"/>
+      <c r="V2" s="10"/>
+      <c r="W2" s="10"/>
+      <c r="X2" s="10"/>
+      <c r="Y2" s="10"/>
     </row>
     <row r="3" spans="1:25">
-      <c r="A3" s="15">
+      <c r="A3" s="12">
         <v>46042</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="12">
         <v>46042</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="13">
         <v>0.5</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="10">
         <v>115</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="10">
         <v>125</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="10">
         <v>122</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="10">
         <v>121</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I3" s="10">
         <v>57.6</v>
       </c>
-      <c r="J3" s="6">
+      <c r="J3" s="10">
         <v>65.8</v>
       </c>
-      <c r="K3" s="6">
+      <c r="K3" s="10">
         <v>63</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="10">
         <v>63</v>
       </c>
-      <c r="M3" s="6">
+      <c r="M3" s="10">
         <v>26.3</v>
       </c>
-      <c r="N3" s="6">
+      <c r="N3" s="10">
         <v>28</v>
       </c>
-      <c r="O3" s="6">
+      <c r="O3" s="10">
         <v>26.8</v>
       </c>
-      <c r="P3" s="6">
+      <c r="P3" s="10">
         <v>26.9</v>
       </c>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="6"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="10"/>
+      <c r="U3" s="10"/>
+      <c r="V3" s="10"/>
+      <c r="W3" s="10"/>
+      <c r="X3" s="10"/>
+      <c r="Y3" s="10"/>
     </row>
     <row r="4" spans="1:25">
-      <c r="A4" s="15">
+      <c r="A4" s="12">
         <v>46077</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="12">
         <v>46077</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="13">
         <v>0.5</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="10">
         <v>117</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="10">
         <v>127</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="10">
         <v>124</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="10">
         <v>122</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="10">
         <v>57.6</v>
       </c>
-      <c r="J4" s="6">
+      <c r="J4" s="10">
         <v>65.8</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4" s="10">
         <v>63</v>
       </c>
-      <c r="L4" s="6">
+      <c r="L4" s="10">
         <v>63</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="10">
         <v>26.2</v>
       </c>
-      <c r="N4" s="6">
+      <c r="N4" s="10">
         <v>27.9</v>
       </c>
-      <c r="O4" s="6">
+      <c r="O4" s="10">
         <v>26.7</v>
       </c>
-      <c r="P4" s="6">
+      <c r="P4" s="10">
         <v>26.8</v>
       </c>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="6"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="10"/>
+      <c r="T4" s="10"/>
+      <c r="U4" s="10"/>
+      <c r="V4" s="10"/>
+      <c r="W4" s="10"/>
+      <c r="X4" s="10"/>
+      <c r="Y4" s="10"/>
     </row>
     <row r="5" spans="1:25">
-      <c r="A5" s="15">
+      <c r="A5" s="12">
         <v>46104</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="12">
         <v>46104</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="13">
         <v>0.5</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5" s="15">
         <v>119</v>
       </c>
-      <c r="F5" s="10">
+      <c r="F5" s="15">
         <v>129</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="15">
         <v>126</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="15">
         <v>124</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="15">
         <v>57.7</v>
       </c>
-      <c r="J5" s="10">
+      <c r="J5" s="15">
         <v>66</v>
       </c>
-      <c r="K5" s="10">
+      <c r="K5" s="15">
         <v>63.1</v>
       </c>
-      <c r="L5" s="10">
+      <c r="L5" s="15">
         <v>63</v>
       </c>
-      <c r="M5" s="10">
+      <c r="M5" s="15">
         <v>26.2</v>
       </c>
-      <c r="N5" s="10">
+      <c r="N5" s="15">
         <v>27.9</v>
       </c>
-      <c r="O5" s="10">
+      <c r="O5" s="15">
         <v>26.7</v>
       </c>
-      <c r="P5" s="10">
+      <c r="P5" s="15">
         <v>26.7</v>
       </c>
     </row>
     <row r="6" spans="1:25">
-      <c r="A6" s="15">
+      <c r="A6" s="12">
         <v>46132</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="12">
         <v>46132</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="13">
         <v>0.5</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="15">
         <v>119</v>
       </c>
-      <c r="F6" s="10">
+      <c r="F6" s="15">
         <v>129</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="15">
         <v>126</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="15">
         <v>126</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="15">
         <v>57.8</v>
       </c>
-      <c r="J6" s="10">
+      <c r="J6" s="15">
         <v>66.2</v>
       </c>
-      <c r="K6" s="10">
+      <c r="K6" s="15">
         <v>63.3</v>
       </c>
-      <c r="L6" s="10">
+      <c r="L6" s="15">
         <v>63.1</v>
       </c>
-      <c r="M6" s="10">
+      <c r="M6" s="15">
         <v>26.2</v>
       </c>
-      <c r="N6" s="10">
+      <c r="N6" s="15">
         <v>27.9</v>
       </c>
-      <c r="O6" s="10">
+      <c r="O6" s="15">
         <v>26.7</v>
       </c>
-      <c r="P6" s="10">
+      <c r="P6" s="15">
         <v>26.7</v>
       </c>
     </row>
     <row r="7" spans="1:25">
-      <c r="A7" s="15">
+      <c r="A7" s="12">
         <v>46162</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="12">
         <v>46162</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="13">
         <v>0.5</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="15">
         <v>119</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="15">
         <v>129</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="15">
         <v>126</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="15">
         <v>126</v>
       </c>
-      <c r="I7" s="10">
+      <c r="I7" s="15">
         <v>57.9</v>
       </c>
-      <c r="J7" s="10">
+      <c r="J7" s="15">
         <v>66.400000000000006</v>
       </c>
-      <c r="K7" s="10">
+      <c r="K7" s="15">
         <v>63.5</v>
       </c>
-      <c r="L7" s="10">
+      <c r="L7" s="15">
         <v>63.3</v>
       </c>
-      <c r="M7" s="10">
+      <c r="M7" s="15">
         <v>26.2</v>
       </c>
-      <c r="N7" s="10">
+      <c r="N7" s="15">
         <v>27.9</v>
       </c>
-      <c r="O7" s="10">
+      <c r="O7" s="15">
         <v>26.7</v>
       </c>
-      <c r="P7" s="10">
+      <c r="P7" s="15">
+        <v>26.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25">
+      <c r="A8" s="12">
+        <v>46195</v>
+      </c>
+      <c r="B8" s="12">
+        <v>46195</v>
+      </c>
+      <c r="C8" s="13">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="E8" s="15">
+        <v>119</v>
+      </c>
+      <c r="F8" s="15">
+        <v>129</v>
+      </c>
+      <c r="G8" s="15">
+        <v>126</v>
+      </c>
+      <c r="H8" s="15">
+        <v>126</v>
+      </c>
+      <c r="I8" s="15">
+        <v>58</v>
+      </c>
+      <c r="J8" s="15">
+        <v>66.400000000000006</v>
+      </c>
+      <c r="K8" s="15">
+        <v>63.6</v>
+      </c>
+      <c r="L8" s="15">
+        <v>63.5</v>
+      </c>
+      <c r="M8" s="15">
+        <v>26.2</v>
+      </c>
+      <c r="N8" s="15">
+        <v>27.9</v>
+      </c>
+      <c r="O8" s="15">
+        <v>26.7</v>
+      </c>
+      <c r="P8" s="15">
         <v>26.7</v>
       </c>
     </row>
@@ -985,365 +1091,365 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12C2B366-3BE4-4AC7-87BD-872D5D27BEBF}">
   <dimension ref="A1:Y8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" style="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="8.6640625" style="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10" style="14" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.44140625" style="14" bestFit="1" customWidth="1"/>
-    <col min="9" max="12" width="11.44140625" style="14" bestFit="1" customWidth="1"/>
-    <col min="13" max="25" width="9" style="10"/>
-    <col min="26" max="16384" width="9" style="7"/>
+    <col min="1" max="1" width="10.08984375" style="27" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6328125" style="27" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.08984375" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.54296875" style="26" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="8.7265625" style="28" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.08984375" style="28" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.54296875" style="28" bestFit="1" customWidth="1"/>
+    <col min="9" max="12" width="11.54296875" style="28" bestFit="1" customWidth="1"/>
+    <col min="13" max="25" width="9" style="29"/>
+    <col min="26" max="16384" width="9" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:25" s="21" customFormat="1">
+      <c r="A1" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="K1" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="L1" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="4"/>
-      <c r="R1" s="4"/>
-      <c r="S1" s="4"/>
-      <c r="T1" s="4"/>
-      <c r="U1" s="4"/>
-      <c r="V1" s="4"/>
-      <c r="W1" s="4"/>
-      <c r="X1" s="4"/>
-      <c r="Y1" s="4"/>
+      <c r="M1" s="30"/>
+      <c r="N1" s="30"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="20"/>
+      <c r="X1" s="20"/>
+      <c r="Y1" s="20"/>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="13" t="s">
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="K2" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="13" t="s">
+      <c r="L2" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
-      <c r="V2" s="6"/>
-      <c r="W2" s="6"/>
-      <c r="X2" s="6"/>
-      <c r="Y2" s="6"/>
+      <c r="M2" s="22"/>
+      <c r="N2" s="22"/>
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
+      <c r="S2" s="22"/>
+      <c r="T2" s="22"/>
+      <c r="U2" s="22"/>
+      <c r="V2" s="22"/>
+      <c r="W2" s="22"/>
+      <c r="X2" s="22"/>
+      <c r="Y2" s="22"/>
     </row>
     <row r="3" spans="1:25">
-      <c r="A3" s="15">
+      <c r="A3" s="27">
         <v>46022</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="27">
         <v>46022</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="25">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="19">
         <v>1.2</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="19">
         <v>1.7</v>
       </c>
-      <c r="G3" s="13">
+      <c r="G3" s="19">
         <v>1.4</v>
       </c>
-      <c r="H3" s="13">
+      <c r="H3" s="19">
         <v>1.4</v>
       </c>
-      <c r="I3" s="13">
+      <c r="I3" s="19">
         <v>5.7</v>
       </c>
-      <c r="J3" s="13">
+      <c r="J3" s="19">
         <v>8.5</v>
       </c>
-      <c r="K3" s="13">
+      <c r="K3" s="19">
         <v>6.8</v>
       </c>
-      <c r="L3" s="13">
+      <c r="L3" s="19">
         <v>6.9</v>
       </c>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="6"/>
+      <c r="M3" s="22"/>
+      <c r="N3" s="22"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22"/>
+      <c r="R3" s="22"/>
+      <c r="S3" s="22"/>
+      <c r="T3" s="22"/>
+      <c r="U3" s="22"/>
+      <c r="V3" s="22"/>
+      <c r="W3" s="22"/>
+      <c r="X3" s="22"/>
+      <c r="Y3" s="22"/>
     </row>
     <row r="4" spans="1:25">
-      <c r="A4" s="15">
+      <c r="A4" s="27">
         <v>46052</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="27">
         <v>46052</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="25">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="19">
         <v>1.2</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="19">
         <v>1.7</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="19">
         <v>1.4</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="19">
         <v>1.4</v>
       </c>
-      <c r="I4" s="13">
+      <c r="I4" s="19">
         <v>5.7</v>
       </c>
-      <c r="J4" s="13">
+      <c r="J4" s="19">
         <v>8.5</v>
       </c>
-      <c r="K4" s="13">
+      <c r="K4" s="19">
         <v>6.7</v>
       </c>
-      <c r="L4" s="13">
+      <c r="L4" s="19">
         <v>6.8</v>
       </c>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="6"/>
+      <c r="M4" s="22"/>
+      <c r="N4" s="22"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22"/>
+      <c r="R4" s="22"/>
+      <c r="S4" s="22"/>
+      <c r="T4" s="22"/>
+      <c r="U4" s="22"/>
+      <c r="V4" s="22"/>
+      <c r="W4" s="22"/>
+      <c r="X4" s="22"/>
+      <c r="Y4" s="22"/>
     </row>
     <row r="5" spans="1:25">
-      <c r="A5" s="15">
+      <c r="A5" s="27">
         <v>46079</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="27">
         <v>46079</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="25">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="28">
         <v>1.2</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="28">
         <v>1.7</v>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="28">
         <v>1.4</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="28">
         <v>1.4</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="28">
         <v>5.7</v>
       </c>
-      <c r="J5" s="14">
+      <c r="J5" s="28">
         <v>8.5</v>
       </c>
-      <c r="K5" s="14">
+      <c r="K5" s="28">
         <v>6.6</v>
       </c>
-      <c r="L5" s="14">
+      <c r="L5" s="28">
         <v>6.7</v>
       </c>
     </row>
     <row r="6" spans="1:25">
-      <c r="A6" s="15">
+      <c r="A6" s="27">
         <v>46111</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="27">
         <v>46111</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="25">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="28">
         <v>1.2</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="28">
         <v>1.7</v>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="28">
         <v>1.4</v>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="28">
         <v>1.4</v>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="28">
         <v>5.7</v>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="28">
         <v>8.5</v>
       </c>
-      <c r="K6" s="14">
+      <c r="K6" s="28">
         <v>6.5</v>
       </c>
-      <c r="L6" s="14">
+      <c r="L6" s="28">
         <v>6.6</v>
       </c>
     </row>
     <row r="7" spans="1:25">
-      <c r="A7" s="15">
+      <c r="A7" s="27">
         <v>46141</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="27">
         <v>46141</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="25">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="28">
         <v>1.2</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="28">
         <v>1.7</v>
       </c>
-      <c r="G7" s="14">
+      <c r="G7" s="28">
         <v>1.4</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H7" s="28">
         <v>1.4</v>
       </c>
-      <c r="I7" s="14">
+      <c r="I7" s="28">
         <v>5.7</v>
       </c>
-      <c r="J7" s="14">
+      <c r="J7" s="28">
         <v>8.5</v>
       </c>
-      <c r="K7" s="14">
+      <c r="K7" s="28">
         <v>6.4</v>
       </c>
-      <c r="L7" s="14">
+      <c r="L7" s="28">
         <v>6.5</v>
       </c>
     </row>
     <row r="8" spans="1:25">
-      <c r="A8" s="15">
+      <c r="A8" s="27">
         <v>46171</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="27">
         <v>46171</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="25">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="28">
         <v>1.2</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="28">
         <v>1.7</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="28">
         <v>1.4</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="28">
         <v>1.4</v>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="28">
         <v>5.7</v>
       </c>
-      <c r="J8" s="14">
+      <c r="J8" s="28">
         <v>8.5</v>
       </c>
-      <c r="K8" s="14">
+      <c r="K8" s="28">
         <v>6.3</v>
       </c>
-      <c r="L8" s="14">
+      <c r="L8" s="28">
         <v>6.4</v>
       </c>
     </row>
@@ -1362,651 +1468,651 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F72FC54-CD8C-473D-B869-CF3F9FC5C7CC}">
   <dimension ref="A1:Y9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" style="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="24" width="8.88671875" style="14" customWidth="1"/>
-    <col min="25" max="25" width="9" style="10"/>
-    <col min="26" max="16384" width="9" style="7"/>
+    <col min="1" max="1" width="10.08984375" style="27" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6328125" style="27" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.08984375" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.54296875" style="26" bestFit="1" customWidth="1"/>
+    <col min="5" max="24" width="8.90625" style="28" customWidth="1"/>
+    <col min="25" max="25" width="9" style="29"/>
+    <col min="26" max="16384" width="9" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:25" s="21" customFormat="1">
+      <c r="A1" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="K1" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="L1" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="13" t="s">
+      <c r="M1" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="13" t="s">
+      <c r="N1" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="O1" s="13" t="s">
+      <c r="O1" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="13" t="s">
+      <c r="P1" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="Q1" s="13" t="s">
+      <c r="Q1" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="R1" s="13" t="s">
+      <c r="R1" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="S1" s="13" t="s">
+      <c r="S1" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="T1" s="13" t="s">
+      <c r="T1" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="13" t="s">
+      <c r="U1" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="V1" s="13" t="s">
+      <c r="V1" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="W1" s="13" t="s">
+      <c r="W1" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="X1" s="13" t="s">
+      <c r="X1" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="Y1" s="4"/>
+      <c r="Y1" s="20"/>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="13" t="s">
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="F2" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="13" t="s">
+      <c r="I2" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="J2" s="13" t="s">
+      <c r="J2" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="K2" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="L2" s="13" t="s">
+      <c r="L2" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="M2" s="13" t="s">
+      <c r="M2" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="N2" s="13" t="s">
+      <c r="N2" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="O2" s="13" t="s">
+      <c r="O2" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="P2" s="13" t="s">
+      <c r="P2" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="Q2" s="13" t="s">
+      <c r="Q2" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="R2" s="13" t="s">
+      <c r="R2" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="S2" s="13" t="s">
+      <c r="S2" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="T2" s="13" t="s">
+      <c r="T2" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="U2" s="13" t="s">
+      <c r="U2" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="V2" s="13" t="s">
+      <c r="V2" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="W2" s="13" t="s">
+      <c r="W2" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="X2" s="13" t="s">
+      <c r="X2" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="Y2" s="6"/>
+      <c r="Y2" s="22"/>
     </row>
     <row r="3" spans="1:25">
-      <c r="A3" s="16">
+      <c r="A3" s="24">
         <v>45991</v>
       </c>
-      <c r="B3" s="16">
+      <c r="B3" s="24">
         <v>45991</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="25">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="19">
         <v>72</v>
       </c>
-      <c r="F3" s="13">
+      <c r="F3" s="19">
         <v>72</v>
       </c>
-      <c r="G3" s="13">
+      <c r="G3" s="19">
         <v>72</v>
       </c>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13">
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19">
         <v>94</v>
       </c>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13">
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
+      <c r="O3" s="19">
         <v>297.5</v>
       </c>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
-      <c r="S3" s="13">
+      <c r="P3" s="19"/>
+      <c r="Q3" s="19"/>
+      <c r="R3" s="19"/>
+      <c r="S3" s="19">
         <v>395.3</v>
       </c>
-      <c r="T3" s="13"/>
-      <c r="U3" s="13"/>
-      <c r="V3" s="13"/>
-      <c r="W3" s="13">
+      <c r="T3" s="19"/>
+      <c r="U3" s="19"/>
+      <c r="V3" s="19"/>
+      <c r="W3" s="19">
         <v>160.4</v>
       </c>
-      <c r="X3" s="13"/>
-      <c r="Y3" s="6"/>
+      <c r="X3" s="19"/>
+      <c r="Y3" s="22"/>
     </row>
     <row r="4" spans="1:25">
-      <c r="A4" s="15">
+      <c r="A4" s="27">
         <v>46022</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="27">
         <v>46022</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="25">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="13">
+      <c r="E4" s="19">
         <v>72.8</v>
       </c>
-      <c r="F4" s="13">
+      <c r="F4" s="19">
         <v>72.8</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="19">
         <v>72.8</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="19">
         <v>72</v>
       </c>
-      <c r="I4" s="13">
+      <c r="I4" s="19">
         <v>91.4</v>
       </c>
-      <c r="J4" s="13">
+      <c r="J4" s="19">
         <v>130</v>
       </c>
-      <c r="K4" s="13">
+      <c r="K4" s="19">
         <v>94.4</v>
       </c>
-      <c r="L4" s="13">
+      <c r="L4" s="19">
         <v>94</v>
       </c>
-      <c r="M4" s="13">
+      <c r="M4" s="19">
         <v>246.7</v>
       </c>
-      <c r="N4" s="13">
+      <c r="N4" s="19">
         <v>305.8</v>
       </c>
-      <c r="O4" s="13">
+      <c r="O4" s="19">
         <v>293.7</v>
       </c>
-      <c r="P4" s="13">
+      <c r="P4" s="19">
         <v>297.5</v>
       </c>
-      <c r="Q4" s="13">
+      <c r="Q4" s="19">
         <v>362.2</v>
       </c>
-      <c r="R4" s="13">
+      <c r="R4" s="19">
         <v>410.1</v>
       </c>
-      <c r="S4" s="13">
+      <c r="S4" s="19">
         <v>387.3</v>
       </c>
-      <c r="T4" s="13">
+      <c r="T4" s="19">
         <v>395.3</v>
       </c>
-      <c r="U4" s="13">
+      <c r="U4" s="19">
         <v>149.19999999999999</v>
       </c>
-      <c r="V4" s="13">
+      <c r="V4" s="19">
         <v>195.1</v>
       </c>
-      <c r="W4" s="13">
+      <c r="W4" s="19">
         <v>160.9</v>
       </c>
-      <c r="X4" s="13">
+      <c r="X4" s="19">
         <v>160.4</v>
       </c>
-      <c r="Y4" s="6"/>
+      <c r="Y4" s="22"/>
     </row>
     <row r="5" spans="1:25">
-      <c r="A5" s="15">
+      <c r="A5" s="27">
         <v>46052</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="27">
         <v>46052</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="25">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="13">
+      <c r="E5" s="19">
         <v>73.599999999999994</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="19">
         <v>73.599999999999994</v>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="19">
         <v>73.599999999999994</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="19">
         <v>72.8</v>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="19">
         <v>94.9</v>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="19">
         <v>142.30000000000001</v>
       </c>
-      <c r="K5" s="13">
+      <c r="K5" s="19">
         <v>96.9</v>
       </c>
-      <c r="L5" s="13">
+      <c r="L5" s="19">
         <v>64.400000000000006</v>
       </c>
-      <c r="M5" s="13">
+      <c r="M5" s="19">
         <v>210</v>
       </c>
-      <c r="N5" s="13">
+      <c r="N5" s="19">
         <v>309.3</v>
       </c>
-      <c r="O5" s="13">
+      <c r="O5" s="19">
         <v>283.3</v>
       </c>
-      <c r="P5" s="13">
+      <c r="P5" s="19">
         <v>293.7</v>
       </c>
-      <c r="Q5" s="13">
+      <c r="Q5" s="19">
         <v>375</v>
       </c>
-      <c r="R5" s="13">
+      <c r="R5" s="19">
         <v>413.8</v>
       </c>
-      <c r="S5" s="13">
+      <c r="S5" s="19">
         <v>391.2</v>
       </c>
-      <c r="T5" s="13">
+      <c r="T5" s="19">
         <v>387.3</v>
       </c>
-      <c r="U5" s="13">
+      <c r="U5" s="19">
         <v>149.80000000000001</v>
       </c>
-      <c r="V5" s="13">
+      <c r="V5" s="19">
         <v>193.2</v>
       </c>
-      <c r="W5" s="13">
+      <c r="W5" s="19">
         <v>161.9</v>
       </c>
-      <c r="X5" s="13">
+      <c r="X5" s="19">
         <v>160.9</v>
       </c>
-      <c r="Y5" s="6"/>
+      <c r="Y5" s="22"/>
     </row>
     <row r="6" spans="1:25">
-      <c r="A6" s="15">
+      <c r="A6" s="27">
         <v>46079</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="27">
         <v>46079</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="25">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="28">
         <v>74.2</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="28">
         <v>74.2</v>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="28">
         <v>74.2</v>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="28">
         <v>73.599999999999994</v>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="28">
         <v>97.3</v>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="28">
         <v>144.80000000000001</v>
       </c>
-      <c r="K6" s="14">
+      <c r="K6" s="28">
         <v>99.4</v>
       </c>
-      <c r="L6" s="14">
+      <c r="L6" s="28">
         <v>96.9</v>
       </c>
-      <c r="M6" s="14">
+      <c r="M6" s="28">
         <v>199.4</v>
       </c>
-      <c r="N6" s="14">
+      <c r="N6" s="28">
         <v>326</v>
       </c>
-      <c r="O6" s="14">
+      <c r="O6" s="28">
         <v>298.10000000000002</v>
       </c>
-      <c r="P6" s="14">
+      <c r="P6" s="28">
         <v>283.3</v>
       </c>
-      <c r="Q6" s="14">
+      <c r="Q6" s="28">
         <v>376.4</v>
       </c>
-      <c r="R6" s="14">
+      <c r="R6" s="28">
         <v>418.4</v>
       </c>
-      <c r="S6" s="14">
+      <c r="S6" s="28">
         <v>406.3</v>
       </c>
-      <c r="T6" s="14">
+      <c r="T6" s="28">
         <v>391.2</v>
       </c>
-      <c r="U6" s="14">
+      <c r="U6" s="28">
         <v>152</v>
       </c>
-      <c r="V6" s="14">
+      <c r="V6" s="28">
         <v>199.1</v>
       </c>
-      <c r="W6" s="14">
+      <c r="W6" s="28">
         <v>161.80000000000001</v>
       </c>
-      <c r="X6" s="14">
+      <c r="X6" s="28">
         <v>161.9</v>
       </c>
     </row>
     <row r="7" spans="1:25">
-      <c r="A7" s="15">
+      <c r="A7" s="27">
         <v>46119</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="27">
         <v>46119</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="25">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="28">
         <v>74.599999999999994</v>
       </c>
-      <c r="F7" s="14">
+      <c r="F7" s="28">
         <v>74.599999999999994</v>
       </c>
-      <c r="G7" s="14">
+      <c r="G7" s="28">
         <v>74.599999999999994</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H7" s="28">
         <v>74.2</v>
       </c>
-      <c r="I7" s="14">
+      <c r="I7" s="28">
         <v>97.9</v>
       </c>
-      <c r="J7" s="14">
+      <c r="J7" s="28">
         <v>158.5</v>
       </c>
-      <c r="K7" s="14">
+      <c r="K7" s="28">
         <v>102.8</v>
       </c>
-      <c r="L7" s="14">
+      <c r="L7" s="28">
         <v>99.4</v>
       </c>
-      <c r="M7" s="14">
+      <c r="M7" s="28">
         <v>210</v>
       </c>
-      <c r="N7" s="14">
+      <c r="N7" s="28">
         <v>327.5</v>
       </c>
-      <c r="O7" s="14">
+      <c r="O7" s="28">
         <v>302.39999999999998</v>
       </c>
-      <c r="P7" s="14">
+      <c r="P7" s="28">
         <v>298.10000000000002</v>
       </c>
-      <c r="Q7" s="14">
+      <c r="Q7" s="28">
         <v>366.5</v>
       </c>
-      <c r="R7" s="14">
+      <c r="R7" s="28">
         <v>423.6</v>
       </c>
-      <c r="S7" s="14">
+      <c r="S7" s="28">
         <v>407</v>
       </c>
-      <c r="T7" s="14">
+      <c r="T7" s="28">
         <v>406.3</v>
       </c>
-      <c r="U7" s="14">
+      <c r="U7" s="28">
         <v>153.6</v>
       </c>
-      <c r="V7" s="14">
+      <c r="V7" s="28">
         <v>211</v>
       </c>
-      <c r="W7" s="14">
+      <c r="W7" s="28">
         <v>169.8</v>
       </c>
-      <c r="X7" s="14">
+      <c r="X7" s="28">
         <v>161.80000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:25">
-      <c r="A8" s="15">
+      <c r="A8" s="27">
         <v>46141</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="27">
         <v>46141</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="25">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="28">
         <v>75.099999999999994</v>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="28">
         <v>75.099999999999994</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="28">
         <v>75.099999999999994</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="28">
         <v>74.599999999999994</v>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="28">
         <v>98.4</v>
       </c>
-      <c r="J8" s="14">
+      <c r="J8" s="28">
         <v>150</v>
       </c>
-      <c r="K8" s="14">
+      <c r="K8" s="28">
         <v>100.6</v>
       </c>
-      <c r="L8" s="14">
+      <c r="L8" s="28">
         <v>102.8</v>
       </c>
-      <c r="M8" s="14">
+      <c r="M8" s="28">
         <v>225</v>
       </c>
-      <c r="N8" s="14">
+      <c r="N8" s="28">
         <v>341.3</v>
       </c>
-      <c r="O8" s="14">
+      <c r="O8" s="28">
         <v>317.39999999999998</v>
       </c>
-      <c r="P8" s="14">
+      <c r="P8" s="28">
         <v>302.39999999999998</v>
       </c>
-      <c r="Q8" s="14">
+      <c r="Q8" s="28">
         <v>373.1</v>
       </c>
-      <c r="R8" s="14">
+      <c r="R8" s="28">
         <v>428.6</v>
       </c>
-      <c r="S8" s="14">
+      <c r="S8" s="28">
         <v>408.9</v>
       </c>
-      <c r="T8" s="14">
+      <c r="T8" s="28">
         <v>407</v>
       </c>
-      <c r="U8" s="14">
+      <c r="U8" s="28">
         <v>152.9</v>
       </c>
-      <c r="V8" s="14">
+      <c r="V8" s="28">
         <v>208</v>
       </c>
-      <c r="W8" s="14">
+      <c r="W8" s="28">
         <v>168.7</v>
       </c>
-      <c r="X8" s="14">
+      <c r="X8" s="28">
         <v>169.8</v>
       </c>
     </row>
     <row r="9" spans="1:25">
-      <c r="A9" s="15">
+      <c r="A9" s="27">
         <v>46171</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="27">
         <v>46171</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="25">
         <v>0.61111111111111105</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="14">
+      <c r="E9" s="28">
         <v>75.5</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="28">
         <v>75.5</v>
       </c>
-      <c r="G9" s="14">
+      <c r="G9" s="28">
         <v>75.5</v>
       </c>
-      <c r="H9" s="14">
+      <c r="H9" s="28">
         <v>75.099999999999994</v>
       </c>
-      <c r="I9" s="14">
+      <c r="I9" s="28">
         <v>98.9</v>
       </c>
-      <c r="J9" s="14">
+      <c r="J9" s="28">
         <v>142.6</v>
       </c>
-      <c r="K9" s="14">
+      <c r="K9" s="28">
         <v>100.7</v>
       </c>
-      <c r="L9" s="14">
+      <c r="L9" s="28">
         <v>100.6</v>
       </c>
-      <c r="M9" s="14">
+      <c r="M9" s="28">
         <v>201.1</v>
       </c>
-      <c r="N9" s="14">
+      <c r="N9" s="28">
         <v>331.4</v>
       </c>
-      <c r="O9" s="14">
+      <c r="O9" s="28">
         <v>302.8</v>
       </c>
-      <c r="P9" s="14">
+      <c r="P9" s="28">
         <v>317.39999999999998</v>
       </c>
-      <c r="Q9" s="14">
+      <c r="Q9" s="28">
         <v>386.9</v>
       </c>
-      <c r="R9" s="14">
+      <c r="R9" s="28">
         <v>437.7</v>
       </c>
-      <c r="S9" s="14">
+      <c r="S9" s="28">
         <v>413.6</v>
       </c>
-      <c r="T9" s="14">
+      <c r="T9" s="28">
         <v>408.9</v>
       </c>
-      <c r="U9" s="14">
+      <c r="U9" s="28">
         <v>152.5</v>
       </c>
-      <c r="V9" s="14">
+      <c r="V9" s="28">
         <v>219.5</v>
       </c>
-      <c r="W9" s="14">
+      <c r="W9" s="28">
         <v>168.5</v>
       </c>
-      <c r="X9" s="14">
+      <c r="X9" s="28">
         <v>168.7</v>
       </c>
     </row>
@@ -2025,407 +2131,451 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{535C5E87-C6BF-4E93-9B61-00AC746AD42A}">
-  <dimension ref="A1:Y8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
+  <dimension ref="A1:Y9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="12.109375" style="15" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.109375" style="15" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.6640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.109375" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.6640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.44140625" style="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.6640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.44140625" style="12" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="11.6640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="25" width="9" style="10"/>
-    <col min="26" max="16384" width="9" style="7"/>
+    <col min="1" max="1" width="10.08984375" style="27" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6328125" style="27" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.08984375" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.54296875" style="26" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.6328125" style="32" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.08984375" style="32" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.6328125" style="32" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.453125" style="32" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.6328125" style="32" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.453125" style="32" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="11.6328125" style="32" bestFit="1" customWidth="1"/>
+    <col min="15" max="25" width="9" style="29"/>
+    <col min="26" max="16384" width="9" style="23"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" s="5" customFormat="1">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:25" s="21" customFormat="1">
+      <c r="A1" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="M1" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="N1" s="11" t="s">
+      <c r="N1" s="31" t="s">
         <v>33</v>
       </c>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="4"/>
+      <c r="O1" s="30"/>
+      <c r="P1" s="30"/>
+      <c r="Q1" s="30"/>
+      <c r="R1" s="30"/>
+      <c r="S1" s="30"/>
+      <c r="T1" s="30"/>
+      <c r="U1" s="30"/>
+      <c r="V1" s="30"/>
+      <c r="W1" s="30"/>
+      <c r="X1" s="30"/>
+      <c r="Y1" s="20"/>
     </row>
     <row r="2" spans="1:25">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="11" t="s">
+      <c r="A2" s="16"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="F2" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="G2" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="I2" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="J2" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="K2" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="L2" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="M2" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="N2" s="11" t="s">
+      <c r="N2" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
-      <c r="V2" s="6"/>
-      <c r="W2" s="6"/>
-      <c r="X2" s="6"/>
-      <c r="Y2" s="6"/>
+      <c r="O2" s="22"/>
+      <c r="P2" s="22"/>
+      <c r="Q2" s="22"/>
+      <c r="R2" s="22"/>
+      <c r="S2" s="22"/>
+      <c r="T2" s="22"/>
+      <c r="U2" s="22"/>
+      <c r="V2" s="22"/>
+      <c r="W2" s="22"/>
+      <c r="X2" s="22"/>
+      <c r="Y2" s="22"/>
     </row>
     <row r="3" spans="1:25">
-      <c r="A3" s="15">
+      <c r="A3" s="27">
         <v>45962</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="25">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="11">
+      <c r="E3" s="31">
         <v>24118</v>
       </c>
-      <c r="F3" s="11">
+      <c r="F3" s="31">
         <v>738</v>
       </c>
-      <c r="G3" s="11">
+      <c r="G3" s="31">
         <v>18186</v>
       </c>
-      <c r="H3" s="11">
+      <c r="H3" s="31">
         <v>1184</v>
       </c>
-      <c r="I3" s="11">
+      <c r="I3" s="31">
         <v>13817</v>
       </c>
-      <c r="J3" s="11">
+      <c r="J3" s="31">
         <v>2638</v>
       </c>
-      <c r="K3" s="11">
+      <c r="K3" s="31">
         <v>20226</v>
       </c>
-      <c r="L3" s="11">
+      <c r="L3" s="31">
         <v>15428</v>
       </c>
-      <c r="M3" s="11">
+      <c r="M3" s="31">
         <v>76347</v>
       </c>
-      <c r="N3" s="11">
+      <c r="N3" s="31">
         <v>19987</v>
       </c>
-      <c r="O3" s="6"/>
-      <c r="P3" s="6"/>
-      <c r="Q3" s="6"/>
-      <c r="R3" s="6"/>
-      <c r="S3" s="6"/>
-      <c r="T3" s="6"/>
-      <c r="U3" s="6"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6"/>
-      <c r="Y3" s="6"/>
+      <c r="O3" s="22"/>
+      <c r="P3" s="22"/>
+      <c r="Q3" s="22"/>
+      <c r="R3" s="22"/>
+      <c r="S3" s="22"/>
+      <c r="T3" s="22"/>
+      <c r="U3" s="22"/>
+      <c r="V3" s="22"/>
+      <c r="W3" s="22"/>
+      <c r="X3" s="22"/>
+      <c r="Y3" s="22"/>
     </row>
     <row r="4" spans="1:25">
-      <c r="A4" s="15">
+      <c r="A4" s="27">
         <v>45992</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="27">
         <v>46042</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="25">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4" s="31">
         <v>26154</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="31">
         <v>786</v>
       </c>
-      <c r="G4" s="11">
+      <c r="G4" s="31">
         <v>20229</v>
       </c>
-      <c r="H4" s="11">
+      <c r="H4" s="31">
         <v>1306</v>
       </c>
-      <c r="I4" s="11">
+      <c r="I4" s="31">
         <v>14924</v>
       </c>
-      <c r="J4" s="11">
+      <c r="J4" s="31">
         <v>2849</v>
       </c>
-      <c r="K4" s="11">
+      <c r="K4" s="31">
         <v>21536</v>
       </c>
-      <c r="L4" s="11">
+      <c r="L4" s="31">
         <v>16649</v>
       </c>
-      <c r="M4" s="11">
+      <c r="M4" s="31">
         <v>82844</v>
       </c>
-      <c r="N4" s="11">
+      <c r="N4" s="31">
         <v>21591</v>
       </c>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="6"/>
-      <c r="T4" s="6"/>
-      <c r="U4" s="6"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6"/>
-      <c r="Y4" s="6"/>
+      <c r="O4" s="22"/>
+      <c r="P4" s="22"/>
+      <c r="Q4" s="22"/>
+      <c r="R4" s="22"/>
+      <c r="S4" s="22"/>
+      <c r="T4" s="22"/>
+      <c r="U4" s="22"/>
+      <c r="V4" s="22"/>
+      <c r="W4" s="22"/>
+      <c r="X4" s="22"/>
+      <c r="Y4" s="22"/>
     </row>
     <row r="5" spans="1:25">
-      <c r="A5" s="15">
-        <v>45658</v>
-      </c>
-      <c r="B5" s="15">
+      <c r="A5" s="27">
+        <v>46023</v>
+      </c>
+      <c r="B5" s="27">
         <v>46079</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="25">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="32">
         <v>21091</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="32">
         <v>591</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="32">
         <v>17998</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="32">
         <v>1163</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="32">
         <v>14139</v>
       </c>
-      <c r="J5" s="12">
+      <c r="J5" s="32">
         <v>2690</v>
       </c>
-      <c r="K5" s="12">
+      <c r="K5" s="32">
         <v>22008</v>
       </c>
-      <c r="L5" s="12">
+      <c r="L5" s="32">
         <v>16619</v>
       </c>
-      <c r="M5" s="12">
+      <c r="M5" s="32">
         <v>75236</v>
       </c>
-      <c r="N5" s="12">
+      <c r="N5" s="32">
         <v>21064</v>
       </c>
     </row>
     <row r="6" spans="1:25">
-      <c r="A6" s="15">
-        <v>45689</v>
-      </c>
-      <c r="B6" s="15">
+      <c r="A6" s="27">
+        <v>46054</v>
+      </c>
+      <c r="B6" s="27">
         <v>46106</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="25">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="12">
+      <c r="E6" s="32">
         <v>19143</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="32">
         <v>552</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="32">
         <v>14885</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="32">
         <v>950</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="32">
         <v>12274</v>
       </c>
-      <c r="J6" s="12">
+      <c r="J6" s="32">
         <v>2362</v>
       </c>
-      <c r="K6" s="12">
+      <c r="K6" s="32">
         <v>18459</v>
       </c>
-      <c r="L6" s="12">
+      <c r="L6" s="32">
         <v>14203</v>
       </c>
-      <c r="M6" s="12">
+      <c r="M6" s="32">
         <v>64762</v>
       </c>
-      <c r="N6" s="12">
+      <c r="N6" s="32">
         <v>18066</v>
       </c>
     </row>
     <row r="7" spans="1:25">
-      <c r="A7" s="15">
-        <v>45717</v>
-      </c>
-      <c r="B7" s="15">
+      <c r="A7" s="27">
+        <v>46082</v>
+      </c>
+      <c r="B7" s="27">
         <v>46133</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="25">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="12">
+      <c r="E7" s="32">
         <v>28900</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="32">
         <v>869</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="32">
         <v>22860</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="32">
         <v>1486</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="32">
         <v>15216</v>
       </c>
-      <c r="J7" s="12">
+      <c r="J7" s="32">
         <v>2934</v>
       </c>
-      <c r="K7" s="12">
+      <c r="K7" s="32">
         <v>21474</v>
       </c>
-      <c r="L7" s="12">
+      <c r="L7" s="32">
         <v>17001</v>
       </c>
-      <c r="M7" s="12">
+      <c r="M7" s="32">
         <v>88450</v>
       </c>
-      <c r="N7" s="12">
+      <c r="N7" s="32">
         <v>22289</v>
       </c>
     </row>
     <row r="8" spans="1:25">
-      <c r="A8" s="15">
-        <v>45748</v>
-      </c>
-      <c r="B8" s="15">
+      <c r="A8" s="27">
+        <v>46113</v>
+      </c>
+      <c r="B8" s="27">
         <v>46162</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="25">
         <v>0.75694444444444453</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="32">
         <v>21757</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="32">
         <v>640</v>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="32">
         <v>17526</v>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="32">
         <v>1137</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="32">
         <v>13612</v>
       </c>
-      <c r="J8" s="12">
+      <c r="J8" s="32">
         <v>2650</v>
       </c>
-      <c r="K8" s="12">
+      <c r="K8" s="32">
         <v>19931</v>
       </c>
-      <c r="L8" s="12">
+      <c r="L8" s="32">
         <v>15627</v>
       </c>
-      <c r="M8" s="12">
+      <c r="M8" s="32">
         <v>72827</v>
       </c>
-      <c r="N8" s="12">
+      <c r="N8" s="32">
         <v>20053</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25">
+      <c r="A9" s="27">
+        <v>46143</v>
+      </c>
+      <c r="B9" s="27">
+        <v>46196</v>
+      </c>
+      <c r="C9" s="25">
+        <v>0.75694444444444453</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="E9" s="32">
+        <v>23916</v>
+      </c>
+      <c r="F9" s="32">
+        <v>720</v>
+      </c>
+      <c r="G9" s="32">
+        <v>19700</v>
+      </c>
+      <c r="H9" s="32">
+        <v>1286</v>
+      </c>
+      <c r="I9" s="32">
+        <v>13895</v>
+      </c>
+      <c r="J9" s="32">
+        <v>2703</v>
+      </c>
+      <c r="K9" s="32">
+        <v>20003</v>
+      </c>
+      <c r="L9" s="32">
+        <v>15457</v>
+      </c>
+      <c r="M9" s="32">
+        <v>77515</v>
+      </c>
+      <c r="N9" s="32">
+        <v>20165</v>
       </c>
     </row>
   </sheetData>
@@ -2443,10 +2593,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="27.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.453125" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.36328125" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
